--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2023,6 +2023,1597 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131389119</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>454167</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7081159</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131389106</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>454075</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7080720</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131389111</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>454083</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7081222</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131389104</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>453958</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7081053</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131389109</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>454299</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7080926</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131389108</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>454186</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7080880</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131389116</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>454023</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7081130</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131389115</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>454066</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7081154</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131389117</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>454074</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7080942</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131389122</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>453952</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7081040</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131389121</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>453956</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7081062</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131389118</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>454198</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7081169</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131389107</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>454033</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7081204</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131389103</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92536</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>454146</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7081178</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131389120</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>454078</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7081226</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131389105</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nymyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>454077</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7080728</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2028,7 +2028,7 @@
         <v>131389119</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389106</v>
+        <v>131389111</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,23 +2138,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2162,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454075</v>
+        <v>454083</v>
       </c>
       <c r="R16" t="n">
-        <v>7080720</v>
+        <v>7081222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,11 +2194,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389111</v>
+        <v>131389106</v>
       </c>
       <c r="B17" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,19 +2231,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2260,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454083</v>
+        <v>454075</v>
       </c>
       <c r="R17" t="n">
-        <v>7081222</v>
+        <v>7080720</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2325,7 +2325,7 @@
         <v>131389104</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>131389109</v>
       </c>
       <c r="B19" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>131389108</v>
       </c>
       <c r="B20" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131389116</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>131389115</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>131389117</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>131389122</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>131389121</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>131389118</v>
       </c>
       <c r="B26" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>131389107</v>
       </c>
       <c r="B27" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131389103</v>
+        <v>131389120</v>
       </c>
       <c r="B28" t="n">
-        <v>92536</v>
+        <v>79248</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454146</v>
+        <v>454078</v>
       </c>
       <c r="R28" t="n">
-        <v>7081178</v>
+        <v>7081226</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3386,6 +3386,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3412,32 +3417,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131389120</v>
+        <v>131389103</v>
       </c>
       <c r="B29" t="n">
-        <v>79246</v>
+        <v>92538</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3447,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454078</v>
+        <v>454146</v>
       </c>
       <c r="R29" t="n">
-        <v>7081226</v>
+        <v>7081178</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,11 +3488,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3517,7 +3517,7 @@
         <v>131389105</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2028,7 +2028,7 @@
         <v>131389119</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389111</v>
+        <v>131389106</v>
       </c>
       <c r="B16" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,19 +2138,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2158,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454083</v>
+        <v>454075</v>
       </c>
       <c r="R16" t="n">
-        <v>7081222</v>
+        <v>7080720</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,6 +2198,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389106</v>
+        <v>131389111</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,23 +2240,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2255,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454075</v>
+        <v>454083</v>
       </c>
       <c r="R17" t="n">
-        <v>7080720</v>
+        <v>7081222</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2325,7 +2325,7 @@
         <v>131389104</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>131389109</v>
       </c>
       <c r="B19" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>131389108</v>
       </c>
       <c r="B20" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131389116</v>
       </c>
       <c r="B21" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>131389115</v>
       </c>
       <c r="B22" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131389117</v>
+        <v>131389122</v>
       </c>
       <c r="B23" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454074</v>
+        <v>453952</v>
       </c>
       <c r="R23" t="n">
-        <v>7080942</v>
+        <v>7081040</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131389122</v>
+        <v>131389117</v>
       </c>
       <c r="B24" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>453952</v>
+        <v>454074</v>
       </c>
       <c r="R24" t="n">
-        <v>7081040</v>
+        <v>7080942</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
         <v>131389121</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>131389118</v>
       </c>
       <c r="B26" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>131389107</v>
       </c>
       <c r="B27" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131389120</v>
+        <v>131389103</v>
       </c>
       <c r="B28" t="n">
-        <v>79248</v>
+        <v>92539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454078</v>
+        <v>454146</v>
       </c>
       <c r="R28" t="n">
-        <v>7081226</v>
+        <v>7081178</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3386,11 +3386,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3417,32 +3412,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131389103</v>
+        <v>131389120</v>
       </c>
       <c r="B29" t="n">
-        <v>92538</v>
+        <v>79249</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,10 +3447,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454146</v>
+        <v>454078</v>
       </c>
       <c r="R29" t="n">
-        <v>7081178</v>
+        <v>7081226</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,6 +3483,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3517,7 +3517,7 @@
         <v>131389105</v>
       </c>
       <c r="B30" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2127,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389106</v>
+        <v>131389111</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,23 +2138,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2162,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454075</v>
+        <v>454083</v>
       </c>
       <c r="R16" t="n">
-        <v>7080720</v>
+        <v>7081222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,11 +2194,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389111</v>
+        <v>131389106</v>
       </c>
       <c r="B17" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,19 +2231,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2260,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454083</v>
+        <v>454075</v>
       </c>
       <c r="R17" t="n">
-        <v>7081222</v>
+        <v>7080720</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2814,7 +2814,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131389122</v>
+        <v>131389117</v>
       </c>
       <c r="B23" t="n">
         <v>79249</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453952</v>
+        <v>454074</v>
       </c>
       <c r="R23" t="n">
-        <v>7081040</v>
+        <v>7080942</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131389117</v>
+        <v>131389122</v>
       </c>
       <c r="B24" t="n">
         <v>79249</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454074</v>
+        <v>453952</v>
       </c>
       <c r="R24" t="n">
-        <v>7080942</v>
+        <v>7081040</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2028,7 +2028,7 @@
         <v>131389119</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>131389111</v>
       </c>
       <c r="B16" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>131389106</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>131389104</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>131389109</v>
       </c>
       <c r="B19" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>131389108</v>
       </c>
       <c r="B20" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131389116</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>131389115</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>131389117</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>131389122</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>131389121</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>131389118</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>131389107</v>
       </c>
       <c r="B27" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>131389103</v>
       </c>
       <c r="B28" t="n">
-        <v>92539</v>
+        <v>92540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>131389120</v>
       </c>
       <c r="B29" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>131389105</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2127,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389111</v>
+        <v>131389106</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,19 +2138,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2158,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454083</v>
+        <v>454075</v>
       </c>
       <c r="R16" t="n">
-        <v>7081222</v>
+        <v>7080720</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,6 +2198,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389106</v>
+        <v>131389111</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,23 +2240,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2255,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454075</v>
+        <v>454083</v>
       </c>
       <c r="R17" t="n">
-        <v>7080720</v>
+        <v>7081222</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -3315,32 +3315,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131389103</v>
+        <v>131389120</v>
       </c>
       <c r="B28" t="n">
-        <v>92540</v>
+        <v>79250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454146</v>
+        <v>454078</v>
       </c>
       <c r="R28" t="n">
-        <v>7081178</v>
+        <v>7081226</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3386,6 +3386,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3412,32 +3417,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131389120</v>
+        <v>131389103</v>
       </c>
       <c r="B29" t="n">
-        <v>79250</v>
+        <v>92540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3447,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454078</v>
+        <v>454146</v>
       </c>
       <c r="R29" t="n">
-        <v>7081226</v>
+        <v>7081178</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,11 +3488,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2028,7 +2028,7 @@
         <v>131389119</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389106</v>
+        <v>131389111</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>91841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,23 +2138,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2162,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454075</v>
+        <v>454083</v>
       </c>
       <c r="R16" t="n">
-        <v>7080720</v>
+        <v>7081222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,11 +2194,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389111</v>
+        <v>131389106</v>
       </c>
       <c r="B17" t="n">
-        <v>91838</v>
+        <v>57891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,19 +2231,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2260,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454083</v>
+        <v>454075</v>
       </c>
       <c r="R17" t="n">
-        <v>7081222</v>
+        <v>7080720</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2325,7 +2325,7 @@
         <v>131389104</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>131389109</v>
       </c>
       <c r="B19" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>131389108</v>
       </c>
       <c r="B20" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131389116</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>131389115</v>
       </c>
       <c r="B22" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>131389117</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>131389122</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>131389121</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>131389118</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>131389107</v>
       </c>
       <c r="B27" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>131389120</v>
       </c>
       <c r="B28" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>131389103</v>
       </c>
       <c r="B29" t="n">
-        <v>92540</v>
+        <v>92543</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>131389105</v>
       </c>
       <c r="B30" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2028,7 +2028,7 @@
         <v>131389119</v>
       </c>
       <c r="B15" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>131389111</v>
       </c>
       <c r="B16" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>131389106</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>131389104</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>131389109</v>
       </c>
       <c r="B19" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>131389108</v>
       </c>
       <c r="B20" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131389116</v>
       </c>
       <c r="B21" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>131389115</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>131389117</v>
       </c>
       <c r="B23" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>131389122</v>
       </c>
       <c r="B24" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>131389121</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>131389118</v>
       </c>
       <c r="B26" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>131389107</v>
       </c>
       <c r="B27" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>131389120</v>
       </c>
       <c r="B28" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>131389103</v>
       </c>
       <c r="B29" t="n">
-        <v>92543</v>
+        <v>92544</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>131389105</v>
       </c>
       <c r="B30" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2028,7 +2028,7 @@
         <v>131389119</v>
       </c>
       <c r="B15" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>131389111</v>
       </c>
       <c r="B16" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>131389106</v>
       </c>
       <c r="B17" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>131389104</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>131389109</v>
       </c>
       <c r="B19" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>131389108</v>
       </c>
       <c r="B20" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131389116</v>
       </c>
       <c r="B21" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>131389115</v>
       </c>
       <c r="B22" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>131389117</v>
       </c>
       <c r="B23" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>131389122</v>
       </c>
       <c r="B24" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>131389121</v>
       </c>
       <c r="B25" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>131389118</v>
       </c>
       <c r="B26" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>131389107</v>
       </c>
       <c r="B27" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131389120</v>
+        <v>131389103</v>
       </c>
       <c r="B28" t="n">
-        <v>79254</v>
+        <v>92550</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454078</v>
+        <v>454146</v>
       </c>
       <c r="R28" t="n">
-        <v>7081226</v>
+        <v>7081178</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3386,11 +3386,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3417,32 +3412,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131389103</v>
+        <v>131389120</v>
       </c>
       <c r="B29" t="n">
-        <v>92544</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,10 +3447,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454146</v>
+        <v>454078</v>
       </c>
       <c r="R29" t="n">
-        <v>7081178</v>
+        <v>7081226</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,6 +3483,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3517,7 +3517,7 @@
         <v>131389105</v>
       </c>
       <c r="B30" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2127,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389111</v>
+        <v>131389106</v>
       </c>
       <c r="B16" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,19 +2138,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2158,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454083</v>
+        <v>454075</v>
       </c>
       <c r="R16" t="n">
-        <v>7081222</v>
+        <v>7080720</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,6 +2198,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389106</v>
+        <v>131389111</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,23 +2240,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2255,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454075</v>
+        <v>454083</v>
       </c>
       <c r="R17" t="n">
-        <v>7080720</v>
+        <v>7081222</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2814,7 +2814,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131389117</v>
+        <v>131389122</v>
       </c>
       <c r="B23" t="n">
         <v>79260</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454074</v>
+        <v>453952</v>
       </c>
       <c r="R23" t="n">
-        <v>7080942</v>
+        <v>7081040</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131389122</v>
+        <v>131389117</v>
       </c>
       <c r="B24" t="n">
         <v>79260</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>453952</v>
+        <v>454074</v>
       </c>
       <c r="R24" t="n">
-        <v>7081040</v>
+        <v>7080942</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131389121</v>
+        <v>131389118</v>
       </c>
       <c r="B25" t="n">
         <v>79260</v>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>453956</v>
+        <v>454198</v>
       </c>
       <c r="R25" t="n">
-        <v>7081062</v>
+        <v>7081169</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3120,7 +3120,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131389118</v>
+        <v>131389121</v>
       </c>
       <c r="B26" t="n">
         <v>79260</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454198</v>
+        <v>453956</v>
       </c>
       <c r="R26" t="n">
-        <v>7081169</v>
+        <v>7081062</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3315,32 +3315,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131389103</v>
+        <v>131389120</v>
       </c>
       <c r="B28" t="n">
-        <v>92550</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454146</v>
+        <v>454078</v>
       </c>
       <c r="R28" t="n">
-        <v>7081178</v>
+        <v>7081226</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3386,6 +3386,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3412,32 +3417,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131389120</v>
+        <v>131389103</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>92551</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3447,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454078</v>
+        <v>454146</v>
       </c>
       <c r="R29" t="n">
-        <v>7081226</v>
+        <v>7081178</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,11 +3488,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2028,7 +2028,7 @@
         <v>131389119</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>131389106</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>131389111</v>
       </c>
       <c r="B17" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>131389104</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>131389109</v>
       </c>
       <c r="B19" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>131389108</v>
       </c>
       <c r="B20" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131389116</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>131389115</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131389122</v>
+        <v>131389117</v>
       </c>
       <c r="B23" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453952</v>
+        <v>454074</v>
       </c>
       <c r="R23" t="n">
-        <v>7081040</v>
+        <v>7080942</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131389117</v>
+        <v>131389122</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454074</v>
+        <v>453952</v>
       </c>
       <c r="R24" t="n">
-        <v>7080942</v>
+        <v>7081040</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,10 +3018,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131389118</v>
+        <v>131389121</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454198</v>
+        <v>453956</v>
       </c>
       <c r="R25" t="n">
-        <v>7081169</v>
+        <v>7081062</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131389121</v>
+        <v>131389118</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>453956</v>
+        <v>454198</v>
       </c>
       <c r="R26" t="n">
-        <v>7081062</v>
+        <v>7081169</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3225,7 +3225,7 @@
         <v>131389107</v>
       </c>
       <c r="B27" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>131389120</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>131389103</v>
       </c>
       <c r="B29" t="n">
-        <v>92551</v>
+        <v>92552</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>131389105</v>
       </c>
       <c r="B30" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -2028,7 +2028,7 @@
         <v>131389119</v>
       </c>
       <c r="B15" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389106</v>
+        <v>131389111</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>91852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,23 +2138,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2162,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454075</v>
+        <v>454083</v>
       </c>
       <c r="R16" t="n">
-        <v>7080720</v>
+        <v>7081222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,11 +2194,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389111</v>
+        <v>131389106</v>
       </c>
       <c r="B17" t="n">
-        <v>91849</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,19 +2231,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2260,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454083</v>
+        <v>454075</v>
       </c>
       <c r="R17" t="n">
-        <v>7081222</v>
+        <v>7080720</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2325,7 +2325,7 @@
         <v>131389104</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>131389109</v>
       </c>
       <c r="B19" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>131389108</v>
       </c>
       <c r="B20" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131389116</v>
       </c>
       <c r="B21" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>131389115</v>
       </c>
       <c r="B22" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>131389117</v>
       </c>
       <c r="B23" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>131389122</v>
       </c>
       <c r="B24" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>131389121</v>
       </c>
       <c r="B25" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>131389118</v>
       </c>
       <c r="B26" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>131389107</v>
       </c>
       <c r="B27" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131389120</v>
+        <v>131389103</v>
       </c>
       <c r="B28" t="n">
-        <v>79261</v>
+        <v>92555</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454078</v>
+        <v>454146</v>
       </c>
       <c r="R28" t="n">
-        <v>7081226</v>
+        <v>7081178</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3386,11 +3386,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3417,32 +3412,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131389103</v>
+        <v>131389120</v>
       </c>
       <c r="B29" t="n">
-        <v>92552</v>
+        <v>79264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,10 +3447,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454146</v>
+        <v>454078</v>
       </c>
       <c r="R29" t="n">
-        <v>7081178</v>
+        <v>7081226</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,6 +3483,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3517,7 +3517,7 @@
         <v>131389105</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79436936</v>
+        <v>127271520</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillbakvattnet, Jmt</t>
+          <t>Nymyren, Nymyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454127.7029725417</v>
+        <v>454203</v>
       </c>
       <c r="R2" t="n">
-        <v>7080751.063357737</v>
+        <v>7080894</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,31 +756,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Bördig och örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89604304</v>
+        <v>127272108</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
+          <t>Nymyren, Nymyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454117.1443137156</v>
+        <v>454176</v>
       </c>
       <c r="R3" t="n">
-        <v>7080723.862940956</v>
+        <v>7081093</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,30 +858,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bördig och örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127272108</v>
+        <v>127273876</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454176</v>
+        <v>454178</v>
       </c>
       <c r="R4" t="n">
-        <v>7081093</v>
+        <v>7080970</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127270666</v>
+        <v>127274223</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454088</v>
+        <v>454141</v>
       </c>
       <c r="R5" t="n">
-        <v>7080851</v>
+        <v>7080903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127274223</v>
+        <v>127273367</v>
       </c>
       <c r="B6" t="n">
-        <v>75158</v>
+        <v>92037</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>3277</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454141</v>
+        <v>453965</v>
       </c>
       <c r="R6" t="n">
-        <v>7080903</v>
+        <v>7081038</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,45 +1185,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127270671</v>
+        <v>131389103</v>
       </c>
       <c r="B7" t="n">
-        <v>75153</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nymyren, Nymyren, Jmt</t>
+          <t>Nymyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454090</v>
+        <v>454146</v>
       </c>
       <c r="R7" t="n">
-        <v>7080854</v>
+        <v>7081178</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1250,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,66 +1266,61 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127271520</v>
+        <v>89604304</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nymyren, Nymyren, Jmt</t>
+          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454203</v>
+        <v>454117</v>
       </c>
       <c r="R8" t="n">
-        <v>7080894</v>
+        <v>7080724</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,12 +1347,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,53 +1363,52 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127273367</v>
+        <v>127270666</v>
       </c>
       <c r="B9" t="n">
-        <v>91470</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3277</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1418,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>453965</v>
+        <v>454088</v>
       </c>
       <c r="R9" t="n">
-        <v>7081038</v>
+        <v>7080851</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,45 +1485,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127273617</v>
+        <v>131389115</v>
       </c>
       <c r="B10" t="n">
-        <v>91368</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nymyren, Nymyren, Jmt</t>
+          <t>Nymyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454109</v>
+        <v>454066</v>
       </c>
       <c r="R10" t="n">
-        <v>7080945</v>
+        <v>7081154</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,12 +1550,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,66 +1571,61 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127271787</v>
+        <v>131389116</v>
       </c>
       <c r="B11" t="n">
-        <v>91368</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nymyren, Nymyren, Jmt</t>
+          <t>Nymyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454278</v>
+        <v>454023</v>
       </c>
       <c r="R11" t="n">
-        <v>7081004</v>
+        <v>7081130</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,12 +1652,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,66 +1673,61 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127273120</v>
+        <v>131389117</v>
       </c>
       <c r="B12" t="n">
-        <v>97551</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220686</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nymyren, Nymyren, Jmt</t>
+          <t>Nymyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454026</v>
+        <v>454074</v>
       </c>
       <c r="R12" t="n">
-        <v>7081151</v>
+        <v>7080942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,12 +1754,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,66 +1775,61 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127273876</v>
+        <v>131389118</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nymyren, Nymyren, Jmt</t>
+          <t>Nymyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454178</v>
+        <v>454198</v>
       </c>
       <c r="R13" t="n">
-        <v>7080970</v>
+        <v>7081169</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,12 +1856,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,66 +1877,61 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127271244</v>
+        <v>131389119</v>
       </c>
       <c r="B14" t="n">
-        <v>91368</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nymyren, Nymyren, Jmt</t>
+          <t>Nymyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454163</v>
+        <v>454167</v>
       </c>
       <c r="R14" t="n">
-        <v>7080984</v>
+        <v>7081159</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1988,12 +1958,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,35 +1979,30 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131389119</v>
+        <v>131389120</v>
       </c>
       <c r="B15" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2060,10 +2030,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454167</v>
+        <v>454078</v>
       </c>
       <c r="R15" t="n">
-        <v>7081159</v>
+        <v>7081226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,30 +2097,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389111</v>
+        <v>131389121</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2158,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454083</v>
+        <v>453956</v>
       </c>
       <c r="R16" t="n">
-        <v>7081222</v>
+        <v>7081062</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,6 +2168,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,32 +2199,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389106</v>
+        <v>131389122</v>
       </c>
       <c r="B17" t="n">
-        <v>57904</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2234,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454075</v>
+        <v>453952</v>
       </c>
       <c r="R17" t="n">
-        <v>7080720</v>
+        <v>7081040</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2295,7 +2274,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,32 +2301,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131389104</v>
+        <v>131389123</v>
       </c>
       <c r="B18" t="n">
-        <v>57904</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>453958</v>
+        <v>454051</v>
       </c>
       <c r="R18" t="n">
-        <v>7081053</v>
+        <v>7080831</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,7 +2376,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,10 +2403,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131389109</v>
+        <v>79436936</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,30 +2414,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nymyren, Jmt</t>
+          <t>Lillbakvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454299</v>
+        <v>454128</v>
       </c>
       <c r="R19" t="n">
-        <v>7080926</v>
+        <v>7080751</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,12 +2468,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2505,22 +2488,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389108</v>
+        <v>127270671</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,30 +2511,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nymyren, Jmt</t>
+          <t>Nymyren, Nymyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454186</v>
+        <v>454090</v>
       </c>
       <c r="R20" t="n">
-        <v>7080880</v>
+        <v>7080854</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,12 +2565,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2594,26 +2581,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Bördig och örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389116</v>
+        <v>131389104</v>
       </c>
       <c r="B21" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2621,21 +2613,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2645,10 +2637,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454023</v>
+        <v>453958</v>
       </c>
       <c r="R21" t="n">
-        <v>7081130</v>
+        <v>7081053</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,7 +2677,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2712,10 +2704,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389115</v>
+        <v>131389105</v>
       </c>
       <c r="B22" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2723,21 +2715,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2747,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454066</v>
+        <v>454077</v>
       </c>
       <c r="R22" t="n">
-        <v>7081154</v>
+        <v>7080728</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2787,7 +2779,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2814,10 +2806,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131389117</v>
+        <v>131389106</v>
       </c>
       <c r="B23" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2825,21 +2817,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2849,10 +2841,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454074</v>
+        <v>454075</v>
       </c>
       <c r="R23" t="n">
-        <v>7080942</v>
+        <v>7080720</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,7 +2881,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2916,45 +2908,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131389122</v>
+        <v>127273120</v>
       </c>
       <c r="B24" t="n">
-        <v>79266</v>
+        <v>98194</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220686</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nymyren, Jmt</t>
+          <t>Nymyren, Nymyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>453952</v>
+        <v>454026</v>
       </c>
       <c r="R24" t="n">
-        <v>7081040</v>
+        <v>7081151</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2981,17 +2973,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3002,617 +2989,24 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Bördig och örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>131389121</v>
-      </c>
-      <c r="B25" t="n">
-        <v>79266</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Nymyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>453956</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7081062</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>131389118</v>
-      </c>
-      <c r="B26" t="n">
-        <v>79266</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Nymyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>454198</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7081169</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>131389107</v>
-      </c>
-      <c r="B27" t="n">
-        <v>91858</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Nymyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>454033</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7081204</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>131389120</v>
-      </c>
-      <c r="B28" t="n">
-        <v>79266</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Nymyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>454078</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7081226</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>131389103</v>
-      </c>
-      <c r="B29" t="n">
-        <v>92561</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Nymyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>454146</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7081178</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>131389105</v>
-      </c>
-      <c r="B30" t="n">
-        <v>57904</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Nymyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>454077</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7080728</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3431-2026 artfynd.xlsx
+++ b/artfynd/A 3431-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271520</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127272108</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273876</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127274223</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273367</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389103</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604304</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127270666</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389115</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1686,6 +1736,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389116</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389117</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389118</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1992,6 +2057,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389119</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2094,6 +2164,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389120</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2196,6 +2271,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389121</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2298,6 +2378,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389122</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2400,6 +2485,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389123</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2497,6 +2587,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436936</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2599,6 +2694,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127270671</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2701,6 +2801,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389104</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389105</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2905,6 +3015,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389106</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3007,8 +3122,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273120</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>